--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-09-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-09-2025.xlsx
@@ -543,12 +543,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.50</t>
+          <t>£10.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.50</t>
+          <t>£10.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff6ceeb1eb5+80197]
+	GetHandleVerifier [0x0x7ff6ceeb1f10+80288]
+	(No symbol) [0x0x7ff6cec302fa]
+	(No symbol) [0x0x7ff6cec87cd7]
+	(No symbol) [0x0x7ff6cec87f9c]
+	(No symbol) [0x0x7ff6cecdba87]
+	(No symbol) [0x0x7ff6cecb03bf]
+	(No symbol) [0x0x7ff6cecd87fb]
+	(No symbol) [0x0x7ff6cecb0153]
+	(No symbol) [0x0x7ff6cec78b02]
+	(No symbol) [0x0x7ff6cec798d3]
+	GetHandleVerifier [0x0x7ff6cf16e83d+2949837]
+	GetHandleVerifier [0x0x7ff6cf168c6a+2926330]
+	GetHandleVerifier [0x0x7ff6cf1886c7+3055959]
+	GetHandleVerifier [0x0x7ff6ceeccfee+191102]
+	GetHandleVerifier [0x0x7ff6ceed50af+224063]
+	GetHandleVerifier [0x0x7ff6ceebaf64+117236]
+	GetHandleVerifier [0x0x7ff6ceebb119+117673]
+	GetHandleVerifier [0x0x7ff6ceea10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -780,12 +780,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£15.38</t>
+          <t>£16.44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -901,17 +901,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.00</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£15.66</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.80</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.80</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£22.58</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£21.88</t>
+          <t>£23.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1264,17 +1264,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£21.62</t>
+          <t>£25.05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£27.35</t>
+          <t>£29.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£27.39</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£29.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a4d7cd7]
+	(No symbol) [0x0x7ff72a4d7f9c]
+	(No symbol) [0x0x7ff72a52ba87]
+	(No symbol) [0x0x7ff72a5003bf]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£36.00</t>
+          <t>£35.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£36.00</t>
+          <t>£35.55</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>£36.31</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Max retries exceeded with url: /products/110mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000002B9ACDEEE10&gt;, 'Connection to www.insulationuk.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1797,1215 +1797,1222 @@
         </is>
       </c>
       <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=140.0.7339.185)
+Stacktrace:
+	GetHandleVerifier [0x0x7ff72a701eb5+80197]
+	GetHandleVerifier [0x0x7ff72a701f10+80288]
+	(No symbol) [0x0x7ff72a4802fa]
+	(No symbol) [0x0x7ff72a47d001]
+	(No symbol) [0x0x7ff72a46da49]
+	(No symbol) [0x0x7ff72a46f821]
+	(No symbol) [0x0x7ff72a46dd66]
+	(No symbol) [0x0x7ff72a46d7b7]
+	(No symbol) [0x0x7ff72a46d47b]
+	(No symbol) [0x0x7ff72a46afec]
+	(No symbol) [0x0x7ff72a46b87c]
+	(No symbol) [0x0x7ff72a4843ca]
+	(No symbol) [0x0x7ff72a5295de]
+	(No symbol) [0x0x7ff72a50037a]
+	(No symbol) [0x0x7ff72a5287fb]
+	(No symbol) [0x0x7ff72a500153]
+	(No symbol) [0x0x7ff72a4c8b02]
+	(No symbol) [0x0x7ff72a4c98d3]
+	GetHandleVerifier [0x0x7ff72a9be83d+2949837]
+	GetHandleVerifier [0x0x7ff72a9b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff72a9d86c7+3055959]
+	GetHandleVerifier [0x0x7ff72a71cfee+191102]
+	GetHandleVerifier [0x0x7ff72a7250af+224063]
+	GetHandleVerifier [0x0x7ff72a70af64+117236]
+	GetHandleVerifier [0x0x7ff72a70b119+117673]
+	GetHandleVerifier [0x0x7ff72a6f10a8+11064]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /110mm_eurethane_gp_pir_insulation_board_recticel.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000002B9ACE20150&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>£44.56</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REC120mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Recticel Eurothane GP 120mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£32.95</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£32.95</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£32.95</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£37.50-Sale Price old price: £44.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>£33.70</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>£33.00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>£43.99 presale price: £72.38</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>£33.72</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>£32.72</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>£88.80</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>£44.56</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>N/L</t>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>£38.95</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>£47.00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>£51.25</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>£37.53</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REC120mm</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Recticel Eurothane GP 120mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£34.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>£34.50</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>£34.50</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£37.50-Sale Price old price: £44.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REC130mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Recticel Eurothane GP 130mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£40.20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>£40.20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>£46.00-Sale Price old price: £59.95</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>POA or OOS</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£33.70</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>£33.00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>£43.99 presale price: £72.38</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>£33.72</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>£32.72</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>£40.25</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>£38.68</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>£55.40 presale price: £82.22</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>£41.10</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>£39.88</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>£38.95</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>£47.00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>£53.54</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>£51.25</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>£37.53</t>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>£59.2</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>N/L</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REC130mm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Recticel Eurothane GP 130mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REC140mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Recticel Eurothane GP 140mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>£41.00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>£41.00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>£46.00-Sale Price old price: £59.95</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>£47.50-Sale Price old price: £60.95</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>POA or OOS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>£40.25</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>£38.68</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>£55.40 presale price: £82.22</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>£41.10</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>£39.88</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>£41.05</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>£41.00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>£58.50 presale price: £87.35</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>£41.93</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>£40.68</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>£38.95</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>£53.54</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>£48.50</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>£57.00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>£59.2</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>£61.3</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>N/L</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REC140mm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Recticel Eurothane GP 140mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£41.50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>£41.50</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>£47.50-Sale Price old price: £60.95</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REC150mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Recticel Eurothane GP 150mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£40.92</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>£40.92</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>£40.92</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>£47.00-Sale Price old price: £53.95</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>POA or OOS</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>£41.05</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>£41.00</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>£58.50 presale price: £87.35</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>£41.93</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>£40.68</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>£40.95</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>£44.55</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>£53.99 presale price: £89.12</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>£41.86</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>£40.62</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>£48.50</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>£57.00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>£48.37</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>£58.00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>£61.3</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>N/L</t>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>£62.4</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>£47.87</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REC150mm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Recticel Eurothane GP 150mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£40.95</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>£40.95</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>£41.50</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>£47.00-Sale Price old price: £53.95</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>reccav40</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Recticel Eurowall Cavity 40mm x 1.2m x 0.45m (24 Sh / 12.96m2)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£183.71</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>£183.71</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>reccav45</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Recticel Eurowall Cavity 50mm x 1.2m x 0.45m (20 Sh / 10.80m2)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£95.21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>£95.21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>POA or OOS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>£40.95</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>£40.40</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>£53.99 presale price: £89.12</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>£41.86</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>£40.62</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>£103.22</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>£101.50</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>£48.37</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>£58.00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>£62.4</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>£47.87</t>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>£98.03</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>reccav40</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Recticel Eurowall Cavity 40mm x 1.2m x 0.45m (24 Sh / 12.96m2)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£183.71</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>£183.71</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>reccav45</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Recticel Eurowall Cavity 50mm x 1.2m x 0.45m (20 Sh / 10.80m2)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£95.21</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>£95.21</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>reccav100</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Recticel Eurowall Cavity 100mm x 1.2m x 0.45m (10 Sh / 5.40m2)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£89.22</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>£89.22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>POA or OOS</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>£103.22</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>£101.50</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>£89.41</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>£87.25</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>£98.03</t>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>£177.99</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>reccav100</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Recticel Eurowall Cavity 100mm x 1.2m x 0.45m (10 Sh / 5.40m2)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£89.22</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>£89.22</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>£89.41</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>£87.25</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>recwepl37.5mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Recticel Eurothane PL 37.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>£177.99</t>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>N/L</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>recwepl37.5mm</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Recticel Eurothane PL 37.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>recwepl52.5mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Recticel Eurothane PL 52.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£46.52</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>£46.52</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>N/L</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>recwepl52.5mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Recticel Eurothane PL 52.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£46.52</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>£46.52</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>recwepl62.5mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Recticel Eurothane PL 62.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£50.16</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>£50.16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
-</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>recwepl62.5mm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Recticel Eurothane PL 62.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£50.16</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>£50.16</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff696131eb5+80197]
+	GetHandleVerifier [0x0x7ff696131f10+80288]
+	(No symbol) [0x0x7ff695eb02fa]
+	(No symbol) [0x0x7ff695f07cd7]
+	(No symbol) [0x0x7ff695f07f9c]
+	(No symbol) [0x0x7ff695f5ba87]
+	(No symbol) [0x0x7ff695f303bf]
+	(No symbol) [0x0x7ff695f587fb]
+	(No symbol) [0x0x7ff695f30153]
+	(No symbol) [0x0x7ff695ef8b02]
+	(No symbol) [0x0x7ff695ef98d3]
+	GetHandleVerifier [0x0x7ff6963ee83d+2949837]
+	GetHandleVerifier [0x0x7ff6963e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6964086c7+3055959]
+	GetHandleVerifier [0x0x7ff69614cfee+191102]
+	GetHandleVerifier [0x0x7ff6961550af+224063]
+	GetHandleVerifier [0x0x7ff69613af64+117236]
+	GetHandleVerifier [0x0x7ff69613b119+117673]
+	GetHandleVerifier [0x0x7ff6961210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
